--- a/JsonConverter/ExcelFiles/WeaponLevel.xlsx
+++ b/JsonConverter/ExcelFiles/WeaponLevel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD3B345-67CB-445D-A874-DCE371368EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB91BBB-72EC-437E-9BA1-9483378335AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29604" yWindow="1260" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="1212" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="24">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,6 +54,86 @@
   </si>
   <si>
     <t>float[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fires 1 more projectile.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Range +40%, Base Damage up by 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Range +20%, Base Damage up by 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Range +20%, Base Damage up by 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Range +100%, Base Damage up by 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Range +100%, Base Damage up by 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passes through 2 more enemy.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 10, Attack Area up by 25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 5, Attack Area up by 10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoolTime reduced by 0.1 secons, Base Damage up by 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoolTime reduced by 0.1 secons, Base Damage up by 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 10, CoolTime reduced by 0.5 secons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Area up by 25%, CoolTime reduced by 0.5 secons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Damage up by 10, Speed up by 20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed up by 30%, Attack Area up by 25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect lasts 0.5 seconds longer., Damage up by 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect lasts 0.5 seconds longer., Base Damage up by 10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -61,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +151,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -120,7 +209,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -402,16 +491,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:F66"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
     <col min="2" max="2" width="9.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.796875" style="1"/>
     <col min="4" max="4" width="31.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="1"/>
+    <col min="5" max="5" width="8.796875" style="1"/>
+    <col min="6" max="6" width="50" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -431,7 +522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="str">
         <f>"Id"</f>
         <v>Id</v>
@@ -457,7 +548,7 @@
         <v>Description</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="str">
         <f>"262159"</f>
         <v>262159</v>
@@ -478,12 +569,11 @@
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="str">
-        <f>"피해량 +10"</f>
-        <v>피해량 +10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="str">
         <f>"362159"</f>
         <v>362159</v>
@@ -504,12 +594,11 @@
         <f>"10,20"</f>
         <v>10,20</v>
       </c>
-      <c r="F5" s="1" t="str">
-        <f>"피해량 +10, 투사체 속도 +20%"</f>
-        <v>피해량 +10, 투사체 속도 +20%</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="str">
         <f>"462159"</f>
         <v>462159</v>
@@ -530,12 +619,11 @@
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="str">
-        <f>"피해량 +10"</f>
-        <v>피해량 +10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="str">
         <f>"562159"</f>
         <v>562159</v>
@@ -556,12 +644,11 @@
         <f>"10,20"</f>
         <v>10,20</v>
       </c>
-      <c r="F7" s="1" t="str">
-        <f>"피해량 +10, 투사체 속도 +20%"</f>
-        <v>피해량 +10, 투사체 속도 +20%</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="str">
         <f>"662159"</f>
         <v>662159</v>
@@ -582,12 +669,11 @@
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="str">
-        <f>"피해량 +10"</f>
-        <v>피해량 +10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="str">
         <f>"762159"</f>
         <v>762159</v>
@@ -608,12 +694,11 @@
         <f>"10,20"</f>
         <v>10,20</v>
       </c>
-      <c r="F9" s="1" t="str">
-        <f>"피해량 +10, 투사체 속도 +20%"</f>
-        <v>피해량 +10, 투사체 속도 +20%</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="str">
         <f>"862159"</f>
         <v>862159</v>
@@ -634,12 +719,11 @@
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="str">
-        <f>"피해량 +10"</f>
-        <v>피해량 +10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="str">
         <f>"262052"</f>
         <v>262052</v>
@@ -660,12 +744,11 @@
         <f>"40,2"</f>
         <v>40,2</v>
       </c>
-      <c r="F11" s="1" t="str">
-        <f>"공격 범위 +40%, 피해량 +2"</f>
-        <v>공격 범위 +40%, 피해량 +2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="str">
         <f>"362052"</f>
         <v>362052</v>
@@ -686,12 +769,11 @@
         <f>"0.1,1"</f>
         <v>0.1,1</v>
       </c>
-      <c r="F12" s="1" t="str">
-        <f>"쿨타임 -0.1, 피해량 +1"</f>
-        <v>쿨타임 -0.1, 피해량 +1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="str">
         <f>"462052"</f>
         <v>462052</v>
@@ -712,12 +794,11 @@
         <f>"20,1"</f>
         <v>20,1</v>
       </c>
-      <c r="F13" s="1" t="str">
-        <f>"공격 범위 +20%, 피해량 +1"</f>
-        <v>공격 범위 +20%, 피해량 +1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="str">
         <f>"562052"</f>
         <v>562052</v>
@@ -738,12 +819,11 @@
         <f>"0.1,2"</f>
         <v>0.1,2</v>
       </c>
-      <c r="F14" s="1" t="str">
-        <f>"쿨타임 -0.1, 피해량 +2"</f>
-        <v>쿨타임 -0.1, 피해량 +2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="str">
         <f>"662052"</f>
         <v>662052</v>
@@ -764,12 +844,11 @@
         <f>"20,1"</f>
         <v>20,1</v>
       </c>
-      <c r="F15" s="1" t="str">
-        <f>"공격 범위 +20%, 피해량 +1"</f>
-        <v>공격 범위 +20%, 피해량 +1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="str">
         <f>"762052"</f>
         <v>762052</v>
@@ -790,12 +869,11 @@
         <f>"0.1,1"</f>
         <v>0.1,1</v>
       </c>
-      <c r="F16" s="1" t="str">
-        <f>"쿨타임 -0.1, 피해량 +1"</f>
-        <v>쿨타임 -0.1, 피해량 +1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="str">
         <f>"862052"</f>
         <v>862052</v>
@@ -816,12 +894,11 @@
         <f>"20,2"</f>
         <v>20,2</v>
       </c>
-      <c r="F17" s="1" t="str">
-        <f>"공격 범위 +20%, 피해량 +2"</f>
-        <v>공격 범위 +20%, 피해량 +2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="str">
         <f>"262059"</f>
         <v>262059</v>
@@ -842,12 +919,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F18" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="str">
         <f>"362059"</f>
         <v>362059</v>
@@ -868,12 +944,11 @@
         <f>"10,0.5"</f>
         <v>10,0.5</v>
       </c>
-      <c r="F19" s="1" t="str">
-        <f>"피해량+10, 쿨타임 -0.5"</f>
-        <v>피해량+10, 쿨타임 -0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="str">
         <f>"462059"</f>
         <v>462059</v>
@@ -894,12 +969,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F20" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="str">
         <f>"562059"</f>
         <v>562059</v>
@@ -920,12 +994,11 @@
         <f>"10,25"</f>
         <v>10,25</v>
       </c>
-      <c r="F21" s="1" t="str">
-        <f>"피해량+10, 공격 범위 +25%"</f>
-        <v>피해량+10, 공격 범위 +25%</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="str">
         <f>"662059"</f>
         <v>662059</v>
@@ -946,12 +1019,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F22" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="str">
         <f>"762059"</f>
         <v>762059</v>
@@ -972,12 +1044,11 @@
         <f>"25,0.5"</f>
         <v>25,0.5</v>
       </c>
-      <c r="F23" s="1" t="str">
-        <f>"공격 범위 +25%, 쿨타임 -0.5"</f>
-        <v>공격 범위 +25%, 쿨타임 -0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F23" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="str">
         <f>"862059"</f>
         <v>862059</v>
@@ -998,12 +1069,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="str">
         <f>"262079"</f>
         <v>262079</v>
@@ -1024,12 +1094,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="str">
         <f>"362079"</f>
         <v>362079</v>
@@ -1050,12 +1119,11 @@
         <f>"30,25"</f>
         <v>30,25</v>
       </c>
-      <c r="F26" s="1" t="str">
-        <f>"투사체 속도 +30%, 공격 범위 +25%"</f>
-        <v>투사체 속도 +30%, 공격 범위 +25%</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="str">
         <f>"462079"</f>
         <v>462079</v>
@@ -1076,12 +1144,11 @@
         <f>"0.5,10"</f>
         <v>0.5,10</v>
       </c>
-      <c r="F27" s="1" t="str">
-        <f>"지속시간 +0.5, 피해량 +10"</f>
-        <v>지속시간 +0.5, 피해량 +10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F27" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="str">
         <f>"562079"</f>
         <v>562079</v>
@@ -1102,12 +1169,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F28" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="str">
         <f>"662079"</f>
         <v>662079</v>
@@ -1128,12 +1194,11 @@
         <f>"30,25"</f>
         <v>30,25</v>
       </c>
-      <c r="F29" s="1" t="str">
-        <f>"투사체 속도 +30%, 공격 범위 +25%"</f>
-        <v>투사체 속도 +30%, 공격 범위 +25%</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="str">
         <f>"762079"</f>
         <v>762079</v>
@@ -1154,12 +1219,11 @@
         <f>"0.5,10"</f>
         <v>0.5,10</v>
       </c>
-      <c r="F30" s="1" t="str">
-        <f>"지속시간 +0.5, 피해량 +10"</f>
-        <v>지속시간 +0.5, 피해량 +10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="str">
         <f>"862079"</f>
         <v>862079</v>
@@ -1180,12 +1244,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F31" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="str">
         <f>"262080"</f>
         <v>262080</v>
@@ -1206,12 +1269,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F32" s="1" t="str">
-        <f>"투사체 +1"</f>
-        <v>투사체 +1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="str">
         <f>"362080"</f>
         <v>362080</v>
@@ -1225,19 +1287,18 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="str">
-        <f>"ProjectileCount,Damage"</f>
-        <v>ProjectileCount,Damage</v>
+        <f>"ProjectileSpeed,Range"</f>
+        <v>ProjectileSpeed,Range</v>
       </c>
       <c r="E33" s="1" t="str">
-        <f>"1,5"</f>
-        <v>1,5</v>
-      </c>
-      <c r="F33" s="1" t="str">
-        <f>"투사체 +1, 피해량 +5"</f>
-        <v>투사체 +1, 피해량 +5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+        <f>"30,25"</f>
+        <v>30,25</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="str">
         <f>"462080"</f>
         <v>462080</v>
@@ -1251,19 +1312,18 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="str">
-        <f>"ProjectileCount,RepeatInterval"</f>
-        <v>ProjectileCount,RepeatInterval</v>
+        <f>"Duration,Damage"</f>
+        <v>Duration,Damage</v>
       </c>
       <c r="E34" s="1" t="str">
-        <f>"1,0.02"</f>
-        <v>1,0.02</v>
-      </c>
-      <c r="F34" s="1" t="str">
-        <f>"투사체 +1, 연사 간격 -0.02"</f>
-        <v>투사체 +1, 연사 간격 -0.02</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+        <f>"0.5,10"</f>
+        <v>0.5,10</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="str">
         <f>"562080"</f>
         <v>562080</v>
@@ -1277,19 +1337,18 @@
         <v>5</v>
       </c>
       <c r="D35" s="1" t="str">
-        <f>"ProjectilePenetration"</f>
-        <v>ProjectilePenetration</v>
+        <f>"ProjectileCount"</f>
+        <v>ProjectileCount</v>
       </c>
       <c r="E35" s="1" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F35" s="1" t="str">
-        <f>"관통 수 +1"</f>
-        <v>관통 수 +1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="str">
         <f>"662080"</f>
         <v>662080</v>
@@ -1303,19 +1362,18 @@
         <v>6</v>
       </c>
       <c r="D36" s="1" t="str">
-        <f>"ProjectileCount,RepeatInterval"</f>
-        <v>ProjectileCount,RepeatInterval</v>
+        <f>"ProjectileSpeed,Range"</f>
+        <v>ProjectileSpeed,Range</v>
       </c>
       <c r="E36" s="1" t="str">
-        <f>"1,0.02"</f>
-        <v>1,0.02</v>
-      </c>
-      <c r="F36" s="1" t="str">
-        <f>"투사체 +1, 연사 간격 -0.02"</f>
-        <v>투사체 +1, 연사 간격 -0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+        <f>"30,25"</f>
+        <v>30,25</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="str">
         <f>"762080"</f>
         <v>762080</v>
@@ -1329,19 +1387,18 @@
         <v>7</v>
       </c>
       <c r="D37" s="1" t="str">
-        <f>"ProjectileCount,Damage"</f>
-        <v>ProjectileCount,Damage</v>
+        <f>"Duration,Damage"</f>
+        <v>Duration,Damage</v>
       </c>
       <c r="E37" s="1" t="str">
-        <f>"1,5"</f>
-        <v>1,5</v>
-      </c>
-      <c r="F37" s="1" t="str">
-        <f>"투사체 +1, 피해량 +5"</f>
-        <v>투사체 +1, 피해량 +5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <f>"0.5,10"</f>
+        <v>0.5,10</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="str">
         <f>"862080"</f>
         <v>862080</v>
@@ -1355,19 +1412,18 @@
         <v>8</v>
       </c>
       <c r="D38" s="1" t="str">
-        <f>"ProjectilePenetration,RepeatInterval"</f>
-        <v>ProjectilePenetration,RepeatInterval</v>
+        <f>"ProjectileCount"</f>
+        <v>ProjectileCount</v>
       </c>
       <c r="E38" s="1" t="str">
-        <f>"1,0.02"</f>
-        <v>1,0.02</v>
-      </c>
-      <c r="F38" s="1" t="str">
-        <f>"관통 수 +1, 연사 간격 -0.02"</f>
-        <v>관통 수 +1, 연사 간격 -0.02</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+        <f>"1"</f>
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="str">
         <f>"262084"</f>
         <v>262084</v>
@@ -1388,12 +1444,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F39" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="str">
         <f>"362084"</f>
         <v>362084</v>
@@ -1414,12 +1469,11 @@
         <f>"100,10"</f>
         <v>100,10</v>
       </c>
-      <c r="F40" s="1" t="str">
-        <f>"공격 범위 +100%, 피해량 +10"</f>
-        <v>공격 범위 +100%, 피해량 +10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F40" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="str">
         <f>"462084"</f>
         <v>462084</v>
@@ -1440,12 +1494,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F41" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="str">
         <f>"562084"</f>
         <v>562084</v>
@@ -1466,12 +1519,11 @@
         <f>"100,20"</f>
         <v>100,20</v>
       </c>
-      <c r="F42" s="1" t="str">
-        <f>"공격 범위 +100%, 피해량 +20"</f>
-        <v>공격 범위 +100%, 피해량 +20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F42" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="str">
         <f>"662084"</f>
         <v>662084</v>
@@ -1492,12 +1544,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F43" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="str">
         <f>"762084"</f>
         <v>762084</v>
@@ -1518,12 +1569,11 @@
         <f>"100,20"</f>
         <v>100,20</v>
       </c>
-      <c r="F44" s="1" t="str">
-        <f>"공격 범위 +100%, 피해량 +20"</f>
-        <v>공격 범위 +100%, 피해량 +20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F44" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="str">
         <f>"862084"</f>
         <v>862084</v>
@@ -1544,12 +1594,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F45" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="str">
         <f>"262160"</f>
         <v>262160</v>
@@ -1570,12 +1619,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F46" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="str">
         <f>"362160"</f>
         <v>362160</v>
@@ -1596,12 +1644,11 @@
         <f>"30,25"</f>
         <v>30,25</v>
       </c>
-      <c r="F47" s="1" t="str">
-        <f>"투사체 속도 +30%, 공격 범위 +25%"</f>
-        <v>투사체 속도 +30%, 공격 범위 +25%</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F47" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="str">
         <f>"462160"</f>
         <v>462160</v>
@@ -1622,12 +1669,11 @@
         <f>"0.5,10"</f>
         <v>0.5,10</v>
       </c>
-      <c r="F48" s="1" t="str">
-        <f>"지속시간 +0.5, 피해량 +10"</f>
-        <v>지속시간 +0.5, 피해량 +10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F48" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="str">
         <f>"562160"</f>
         <v>562160</v>
@@ -1648,12 +1694,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F49" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F49" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="str">
         <f>"662160"</f>
         <v>662160</v>
@@ -1674,12 +1719,11 @@
         <f>"30,25"</f>
         <v>30,25</v>
       </c>
-      <c r="F50" s="1" t="str">
-        <f>"투사체 속도 +30%, 공격 범위 +25%"</f>
-        <v>투사체 속도 +30%, 공격 범위 +25%</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F50" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="str">
         <f>"762160"</f>
         <v>762160</v>
@@ -1700,12 +1744,11 @@
         <f>"0.5,10"</f>
         <v>0.5,10</v>
       </c>
-      <c r="F51" s="1" t="str">
-        <f>"지속시간 +0.5, 피해량 +10"</f>
-        <v>지속시간 +0.5, 피해량 +10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F51" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="str">
         <f>"862160"</f>
         <v>862160</v>
@@ -1726,12 +1769,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F52" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F52" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="str">
         <f>"262158"</f>
         <v>262158</v>
@@ -1752,12 +1794,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F53" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F53" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="str">
         <f>"362158"</f>
         <v>362158</v>
@@ -1778,12 +1819,11 @@
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="F54" s="1" t="str">
-        <f>"피해량 +5"</f>
-        <v>피해량 +5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="str">
         <f>"462158"</f>
         <v>462158</v>
@@ -1804,12 +1844,11 @@
         <f>"5,10"</f>
         <v>5,10</v>
       </c>
-      <c r="F55" s="1" t="str">
-        <f>"피해량 +5, 공격 범위 +10%"</f>
-        <v>피해량 +5, 공격 범위 +10%</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F55" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="str">
         <f>"562158"</f>
         <v>562158</v>
@@ -1830,12 +1869,11 @@
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="F56" s="1" t="str">
-        <f>"피해량 +5"</f>
-        <v>피해량 +5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="str">
         <f>"662158"</f>
         <v>662158</v>
@@ -1856,12 +1894,11 @@
         <f>"5,10"</f>
         <v>5,10</v>
       </c>
-      <c r="F57" s="1" t="str">
-        <f>"피해량 +5, 공격 범위 +10%"</f>
-        <v>피해량 +5, 공격 범위 +10%</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F57" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="str">
         <f>"762158"</f>
         <v>762158</v>
@@ -1882,12 +1919,11 @@
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="F58" s="1" t="str">
-        <f>"피해량 +5"</f>
-        <v>피해량 +5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="str">
         <f>"862158"</f>
         <v>862158</v>
@@ -1908,12 +1944,11 @@
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="F59" s="1" t="str">
-        <f>"피해량 +5"</f>
-        <v>피해량 +5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="str">
         <f>"262161"</f>
         <v>262161</v>
@@ -1934,12 +1969,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F60" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="str">
         <f>"362161"</f>
         <v>362161</v>
@@ -1960,12 +1994,11 @@
         <f>"20"</f>
         <v>20</v>
       </c>
-      <c r="F61" s="1" t="str">
-        <f>"피해량 +20"</f>
-        <v>피해량 +20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F61" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="str">
         <f>"462161"</f>
         <v>462161</v>
@@ -1986,12 +2019,11 @@
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="F62" s="1" t="str">
-        <f>"관통 수 +2"</f>
-        <v>관통 수 +2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="str">
         <f>"562161"</f>
         <v>562161</v>
@@ -2012,12 +2044,11 @@
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="F63" s="1" t="str">
-        <f>"투사체 수 +1"</f>
-        <v>투사체 수 +1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="str">
         <f>"662161"</f>
         <v>662161</v>
@@ -2038,12 +2069,11 @@
         <f>"20"</f>
         <v>20</v>
       </c>
-      <c r="F64" s="1" t="str">
-        <f>"피해량 +20"</f>
-        <v>피해량 +20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F64" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="str">
         <f>"762161"</f>
         <v>762161</v>
@@ -2064,12 +2094,11 @@
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="F65" s="1" t="str">
-        <f>"관통 수 +2"</f>
-        <v>관통 수 +2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="str">
         <f>"862161"</f>
         <v>862161</v>
@@ -2090,9 +2119,8 @@
         <f>"20"</f>
         <v>20</v>
       </c>
-      <c r="F66" s="1" t="str">
-        <f>"피해량 +20"</f>
-        <v>피해량 +20</v>
+      <c r="F66" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/WeaponLevel.xlsx
+++ b/JsonConverter/ExcelFiles/WeaponLevel.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB91BBB-72EC-437E-9BA1-9483378335AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="1212" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="3828" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
